--- a/output_plant/stomata_Intermediate_londono_2018.xlsx
+++ b/output_plant/stomata_Intermediate_londono_2018.xlsx
@@ -609,7 +609,7 @@
     <t xml:space="preserve">10.1002/ajb2.1187</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/stomata-franks_londono_2018.xlsx</t>
+    <t xml:space="preserve">stomata-franks_londono_2018_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
